--- a/XLSX_DATA/RAW_DATA/PAK_raw_data.xlsx
+++ b/XLSX_DATA/RAW_DATA/PAK_raw_data.xlsx
@@ -449,12 +449,12 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>gini</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>log_gdp_pc</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>gini</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
@@ -502,10 +502,10 @@
       <c r="F2" t="n">
         <v>1028.96592446155</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="n">
         <v>6.936309620088013</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
         <v>21.3232921847751</v>
       </c>
@@ -542,10 +542,10 @@
         <v>1047.88663514614</v>
       </c>
       <c r="G3" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="H3" t="n">
         <v>6.954530686459436</v>
-      </c>
-      <c r="H3" t="n">
-        <v>28.7</v>
       </c>
       <c r="I3" t="n">
         <v>21.9943844205166</v>
@@ -582,10 +582,10 @@
       <c r="F4" t="n">
         <v>1028.99804758369</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="n">
         <v>6.936340838440306</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
         <v>21.5572792952471</v>
       </c>
@@ -622,10 +622,10 @@
         <v>1026.50033720969</v>
       </c>
       <c r="G5" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="H5" t="n">
         <v>6.93391056496326</v>
-      </c>
-      <c r="H5" t="n">
-        <v>33.1</v>
       </c>
       <c r="I5" t="n">
         <v>22.0530195066132</v>
@@ -662,10 +662,10 @@
       <c r="F6" t="n">
         <v>1035.49888206288</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="n">
         <v>6.942638601224124</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
         <v>22.103173212169</v>
       </c>
@@ -701,10 +701,10 @@
       <c r="F7" t="n">
         <v>1049.54229686852</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="n">
         <v>6.956109440371903</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
         <v>17.1836347813683</v>
       </c>
@@ -741,10 +741,10 @@
         <v>1057.86767778646</v>
       </c>
       <c r="G8" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="H8" t="n">
         <v>6.964010536341795</v>
-      </c>
-      <c r="H8" t="n">
-        <v>28.7</v>
       </c>
       <c r="I8" t="n">
         <v>17.5934942779914</v>
@@ -781,10 +781,10 @@
       <c r="F9" t="n">
         <v>1059.04171024589</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="n">
         <v>6.965119731271381</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
         <v>17.1588876671988</v>
       </c>
@@ -822,10 +822,10 @@
       <c r="F10" t="n">
         <v>1090.27523993746</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="n">
         <v>6.994185457051062</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
         <v>17.3885833649452</v>
       </c>
@@ -864,10 +864,10 @@
         <v>1146.99632842666</v>
       </c>
       <c r="G11" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="H11" t="n">
         <v>7.044901916101283</v>
-      </c>
-      <c r="H11" t="n">
-        <v>30.9</v>
       </c>
       <c r="I11" t="n">
         <v>18.9071452885794</v>
@@ -907,10 +907,10 @@
         <v>1201.23359367214</v>
       </c>
       <c r="G12" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="H12" t="n">
         <v>7.091104302478136</v>
-      </c>
-      <c r="H12" t="n">
-        <v>31.3</v>
       </c>
       <c r="I12" t="n">
         <v>19.9330293059047</v>
@@ -949,10 +949,10 @@
       <c r="F13" t="n">
         <v>1243.94142602543</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="n">
         <v>7.126040187002022</v>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
         <v>20.199119664936</v>
       </c>
@@ -991,10 +991,10 @@
         <v>1265.35567539842</v>
       </c>
       <c r="G14" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="H14" t="n">
         <v>7.14310852796464</v>
-      </c>
-      <c r="H14" t="n">
-        <v>29.7</v>
       </c>
       <c r="I14" t="n">
         <v>19.9449553163591</v>
@@ -1033,10 +1033,10 @@
       <c r="F15" t="n">
         <v>1258.05188934452</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="n">
         <v>7.137319683901401</v>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
         <v>21.1955484525846</v>
       </c>
@@ -1074,10 +1074,10 @@
       <c r="F16" t="n">
         <v>1269.07432116444</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="n">
         <v>7.146043032716872</v>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
         <v>20.3372467582902</v>
       </c>
@@ -1116,10 +1116,10 @@
         <v>1256.69482201323</v>
       </c>
       <c r="G17" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="H17" t="n">
         <v>7.136240396308027</v>
-      </c>
-      <c r="H17" t="n">
-        <v>28.8</v>
       </c>
       <c r="I17" t="n">
         <v>20.9650197800876</v>
@@ -1159,10 +1159,10 @@
         <v>1261.83161907857</v>
       </c>
       <c r="G18" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="H18" t="n">
         <v>7.140319610331392</v>
-      </c>
-      <c r="H18" t="n">
-        <v>29.7</v>
       </c>
       <c r="I18" t="n">
         <v>21.1864809532945</v>
@@ -1201,10 +1201,10 @@
       <c r="F19" t="n">
         <v>1275.48806898966</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="n">
         <v>7.151084183551179</v>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
         <v>21.9583720724829</v>
       </c>
@@ -1243,10 +1243,10 @@
         <v>1309.70080446386</v>
       </c>
       <c r="G20" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="H20" t="n">
         <v>7.177553996570383</v>
-      </c>
-      <c r="H20" t="n">
-        <v>29.5</v>
       </c>
       <c r="I20" t="n">
         <v>20.8910295084645</v>
@@ -1285,10 +1285,10 @@
       <c r="F21" t="n">
         <v>1343.30778121043</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="n">
         <v>7.202890344660267</v>
       </c>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
         <v>20.8659912298838</v>
       </c>
@@ -1327,10 +1327,10 @@
         <v>1380.47020838317</v>
       </c>
       <c r="G22" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="H22" t="n">
         <v>7.230179450828166</v>
-      </c>
-      <c r="H22" t="n">
-        <v>31.3</v>
       </c>
       <c r="I22" t="n">
         <v>19.602614668814</v>
@@ -1369,10 +1369,10 @@
       <c r="F23" t="n">
         <v>1452.18658269177</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="n">
         <v>7.280825687605688</v>
       </c>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
         <v>18.1501179723214</v>
       </c>
@@ -1410,10 +1410,10 @@
       <c r="F24" t="n">
         <v>1495.26187528032</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="n">
         <v>7.310056637896352</v>
       </c>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
         <v>18.0993270885214</v>
       </c>
@@ -1452,10 +1452,10 @@
         <v>1561.68169819559</v>
       </c>
       <c r="G25" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="H25" t="n">
         <v>7.3535185312701</v>
-      </c>
-      <c r="H25" t="n">
-        <v>29.6</v>
       </c>
       <c r="I25" t="n">
         <v>18.5890515927482</v>
@@ -1494,10 +1494,10 @@
       <c r="F26" t="n">
         <v>1573.8330826937</v>
       </c>
-      <c r="G26" t="n">
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="n">
         <v>7.36126937678076</v>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
         <v>19.5638945814483</v>
       </c>
@@ -1533,10 +1533,10 @@
       <c r="F27" t="n">
         <v>1526.00597486307</v>
       </c>
-      <c r="G27" t="n">
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="n">
         <v>7.330409127212275</v>
       </c>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
         <v>18.5894635445816</v>
       </c>
@@ -1574,10 +1574,10 @@
       <c r="F28" t="n">
         <v>1595.02792175422</v>
       </c>
-      <c r="G28" t="n">
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="n">
         <v>7.374646520867739</v>
       </c>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="n">
         <v>18.8964082009484</v>
       </c>
@@ -1615,10 +1615,10 @@
       <c r="F29" t="n">
         <v>1642.28066974826</v>
       </c>
-      <c r="G29" t="n">
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="n">
         <v>7.403841207042412</v>
       </c>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
         <v>20.4125955543613</v>
       </c>
@@ -1656,10 +1656,10 @@
       <c r="F30" t="n">
         <v>1610.33122837537</v>
       </c>
-      <c r="G30" t="n">
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="n">
         <v>7.384195168728769</v>
       </c>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
         <v>20.718694602313</v>
       </c>
@@ -1698,10 +1698,10 @@
         <v>1634.56735260799</v>
       </c>
       <c r="G31" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="H31" t="n">
         <v>7.399133432172423</v>
-      </c>
-      <c r="H31" t="n">
-        <v>33.5</v>
       </c>
       <c r="I31" t="n">
         <v>20.2457551236068</v>

--- a/XLSX_DATA/RAW_DATA/PAK_raw_data.xlsx
+++ b/XLSX_DATA/RAW_DATA/PAK_raw_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:P32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,6 +482,21 @@
           <t>palma_ratio</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>va_score</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>cc_score</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>ge_score</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -521,8 +536,11 @@
         <v>31.6870914038941</v>
       </c>
       <c r="M2" t="n">
-        <v>3.878679750223015</v>
-      </c>
+        <v>3.671564390665514</v>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -562,8 +580,11 @@
         <v>31.9144613917436</v>
       </c>
       <c r="M3" t="n">
-        <v>4.140221402214022</v>
-      </c>
+        <v>3.595076400679117</v>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -603,7 +624,16 @@
         <v>32.1402116675762</v>
       </c>
       <c r="M4" t="n">
-        <v>4.153061224489796</v>
+        <v>3.521267723102585</v>
+      </c>
+      <c r="N4" t="n">
+        <v>39.79</v>
+      </c>
+      <c r="O4" t="n">
+        <v>24.45</v>
+      </c>
+      <c r="P4" t="n">
+        <v>40.83</v>
       </c>
     </row>
     <row r="5">
@@ -644,8 +674,11 @@
         <v>32.3647607033211</v>
       </c>
       <c r="M5" t="n">
-        <v>4.171802054154995</v>
-      </c>
+        <v>3.904424778761062</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -685,7 +718,16 @@
         <v>32.5871723893723</v>
       </c>
       <c r="M6" t="n">
-        <v>4.175257731958763</v>
+        <v>4.308630393996247</v>
+      </c>
+      <c r="N6" t="n">
+        <v>38.86</v>
+      </c>
+      <c r="O6" t="n">
+        <v>31.65</v>
+      </c>
+      <c r="P6" t="n">
+        <v>40.75</v>
       </c>
     </row>
     <row r="7">
@@ -726,8 +768,11 @@
         <v>32.8015812487933</v>
       </c>
       <c r="M7" t="n">
-        <v>4.226755218216319</v>
-      </c>
+        <v>4.199443413729128</v>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -767,7 +812,16 @@
         <v>33.0046884491535</v>
       </c>
       <c r="M8" t="n">
-        <v>4.245229007633588</v>
+        <v>4.054644808743169</v>
+      </c>
+      <c r="N8" t="n">
+        <v>33.12</v>
+      </c>
+      <c r="O8" t="n">
+        <v>28.13</v>
+      </c>
+      <c r="P8" t="n">
+        <v>40.77</v>
       </c>
     </row>
     <row r="9">
@@ -808,8 +862,11 @@
         <v>33.1988471664032</v>
       </c>
       <c r="M9" t="n">
-        <v>4.262906309751434</v>
-      </c>
+        <v>3.902678571428571</v>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -849,7 +906,16 @@
         <v>33.3857078542752</v>
       </c>
       <c r="M10" t="n">
-        <v>4.35631067961165</v>
+        <v>4.085793357933579</v>
+      </c>
+      <c r="N10" t="n">
+        <v>35.38</v>
+      </c>
+      <c r="O10" t="n">
+        <v>29.36</v>
+      </c>
+      <c r="P10" t="n">
+        <v>39.54</v>
       </c>
     </row>
     <row r="11">
@@ -892,7 +958,16 @@
         <v>33.5669209665019</v>
       </c>
       <c r="M11" t="n">
-        <v>4.486111111111111</v>
+        <v>4.301724137931034</v>
+      </c>
+      <c r="N11" t="n">
+        <v>35.91</v>
+      </c>
+      <c r="O11" t="n">
+        <v>29.18</v>
+      </c>
+      <c r="P11" t="n">
+        <v>35.91</v>
       </c>
     </row>
     <row r="12">
@@ -935,7 +1010,16 @@
         <v>33.7441369568158</v>
       </c>
       <c r="M12" t="n">
-        <v>4.509452736318408</v>
+        <v>4.405063291139241</v>
+      </c>
+      <c r="N12" t="n">
+        <v>35.04</v>
+      </c>
+      <c r="O12" t="n">
+        <v>25.83</v>
+      </c>
+      <c r="P12" t="n">
+        <v>38.56</v>
       </c>
     </row>
     <row r="13">
@@ -978,7 +1062,16 @@
         <v>33.9190062789495</v>
       </c>
       <c r="M13" t="n">
-        <v>4.557114228456913</v>
+        <v>4.669322709163348</v>
+      </c>
+      <c r="N13" t="n">
+        <v>37.16</v>
+      </c>
+      <c r="O13" t="n">
+        <v>26.11</v>
+      </c>
+      <c r="P13" t="n">
+        <v>38.83</v>
       </c>
     </row>
     <row r="14">
@@ -1021,7 +1114,16 @@
         <v>34.0931793866356</v>
       </c>
       <c r="M14" t="n">
-        <v>4.481628599801391</v>
+        <v>4.372115384615385</v>
+      </c>
+      <c r="N14" t="n">
+        <v>40.96</v>
+      </c>
+      <c r="O14" t="n">
+        <v>30.02</v>
+      </c>
+      <c r="P14" t="n">
+        <v>40.9</v>
       </c>
     </row>
     <row r="15">
@@ -1064,7 +1166,16 @@
         <v>34.2683067336065</v>
       </c>
       <c r="M15" t="n">
-        <v>4.447968285431119</v>
+        <v>4.113805970149254</v>
+      </c>
+      <c r="N15" t="n">
+        <v>39.47</v>
+      </c>
+      <c r="O15" t="n">
+        <v>30.73</v>
+      </c>
+      <c r="P15" t="n">
+        <v>41.07</v>
       </c>
     </row>
     <row r="16">
@@ -1107,7 +1218,16 @@
         <v>34.4460387735948</v>
       </c>
       <c r="M16" t="n">
-        <v>4.177251184834123</v>
+        <v>3.861730597680642</v>
+      </c>
+      <c r="N16" t="n">
+        <v>39.97</v>
+      </c>
+      <c r="O16" t="n">
+        <v>26.84</v>
+      </c>
+      <c r="P16" t="n">
+        <v>35.92</v>
       </c>
     </row>
     <row r="17">
@@ -1150,7 +1270,16 @@
         <v>34.6280259603331</v>
       </c>
       <c r="M17" t="n">
-        <v>4.06145251396648</v>
+        <v>3.747156605424322</v>
+      </c>
+      <c r="N17" t="n">
+        <v>40.47</v>
+      </c>
+      <c r="O17" t="n">
+        <v>24</v>
+      </c>
+      <c r="P17" t="n">
+        <v>36.2</v>
       </c>
     </row>
     <row r="18">
@@ -1193,7 +1322,16 @@
         <v>34.8159187475539</v>
       </c>
       <c r="M18" t="n">
-        <v>4.108286252354049</v>
+        <v>3.792035398230088</v>
+      </c>
+      <c r="N18" t="n">
+        <v>41.52</v>
+      </c>
+      <c r="O18" t="n">
+        <v>23.52</v>
+      </c>
+      <c r="P18" t="n">
+        <v>36.23</v>
       </c>
     </row>
     <row r="19">
@@ -1236,7 +1374,16 @@
         <v>35.0113675889897</v>
       </c>
       <c r="M19" t="n">
-        <v>3.997229916897507</v>
+        <v>3.787905346187555</v>
+      </c>
+      <c r="N19" t="n">
+        <v>39.94</v>
+      </c>
+      <c r="O19" t="n">
+        <v>23.15</v>
+      </c>
+      <c r="P19" t="n">
+        <v>35.29</v>
       </c>
     </row>
     <row r="20">
@@ -1279,7 +1426,16 @@
         <v>35.2160229383731</v>
       </c>
       <c r="M20" t="n">
-        <v>3.959633027522936</v>
+        <v>3.724498692240628</v>
+      </c>
+      <c r="N20" t="n">
+        <v>40.09</v>
+      </c>
+      <c r="O20" t="n">
+        <v>22.65</v>
+      </c>
+      <c r="P20" t="n">
+        <v>38.7</v>
       </c>
     </row>
     <row r="21">
@@ -1322,7 +1478,16 @@
         <v>35.4315352494366</v>
       </c>
       <c r="M21" t="n">
-        <v>3.918032786885246</v>
+        <v>3.649653979238754</v>
+      </c>
+      <c r="N21" t="n">
+        <v>40.53</v>
+      </c>
+      <c r="O21" t="n">
+        <v>25</v>
+      </c>
+      <c r="P21" t="n">
+        <v>38.51</v>
       </c>
     </row>
     <row r="22">
@@ -1365,7 +1530,16 @@
         <v>35.6595549759128</v>
       </c>
       <c r="M22" t="n">
-        <v>3.848920863309353</v>
+        <v>3.807929515418502</v>
+      </c>
+      <c r="N22" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="O22" t="n">
+        <v>27.52</v>
+      </c>
+      <c r="P22" t="n">
+        <v>38.08</v>
       </c>
     </row>
     <row r="23">
@@ -1408,7 +1582,16 @@
         <v>35.9017325715342</v>
       </c>
       <c r="M23" t="n">
-        <v>3.749338040600177</v>
+        <v>3.923487544483986</v>
+      </c>
+      <c r="N23" t="n">
+        <v>42.27</v>
+      </c>
+      <c r="O23" t="n">
+        <v>28</v>
+      </c>
+      <c r="P23" t="n">
+        <v>39.47</v>
       </c>
     </row>
     <row r="24">
@@ -1451,7 +1634,16 @@
         <v>36.1597184900333</v>
       </c>
       <c r="M24" t="n">
-        <v>3.724956063268893</v>
+        <v>3.836411609498681</v>
+      </c>
+      <c r="N24" t="n">
+        <v>42.43</v>
+      </c>
+      <c r="O24" t="n">
+        <v>28.16</v>
+      </c>
+      <c r="P24" t="n">
+        <v>41.03</v>
       </c>
     </row>
     <row r="25">
@@ -1494,7 +1686,16 @@
         <v>36.4351548223399</v>
       </c>
       <c r="M25" t="n">
-        <v>3.729111697449429</v>
+        <v>3.767218831734961</v>
+      </c>
+      <c r="N25" t="n">
+        <v>42.52</v>
+      </c>
+      <c r="O25" t="n">
+        <v>28.93</v>
+      </c>
+      <c r="P25" t="n">
+        <v>43.15</v>
       </c>
     </row>
     <row r="26">
@@ -1537,7 +1738,16 @@
         <v>36.7478511550359</v>
       </c>
       <c r="M26" t="n">
-        <v>3.729111697449429</v>
+        <v>3.700086430423509</v>
+      </c>
+      <c r="N26" t="n">
+        <v>42.33</v>
+      </c>
+      <c r="O26" t="n">
+        <v>28.34</v>
+      </c>
+      <c r="P26" t="n">
+        <v>41.48</v>
       </c>
     </row>
     <row r="27">
@@ -1580,7 +1790,16 @@
         <v>37.1091631735769</v>
       </c>
       <c r="M27" t="n">
-        <v>3.729111697449429</v>
+        <v>3.700086430423509</v>
+      </c>
+      <c r="N27" t="n">
+        <v>41.03</v>
+      </c>
+      <c r="O27" t="n">
+        <v>28.19</v>
+      </c>
+      <c r="P27" t="n">
+        <v>41.68</v>
       </c>
     </row>
     <row r="28">
@@ -1621,7 +1840,16 @@
         <v>37.5080192948099</v>
       </c>
       <c r="M28" t="n">
-        <v>3.729111697449429</v>
+        <v>3.700086430423509</v>
+      </c>
+      <c r="N28" t="n">
+        <v>41.57</v>
+      </c>
+      <c r="O28" t="n">
+        <v>28.89</v>
+      </c>
+      <c r="P28" t="n">
+        <v>39.38</v>
       </c>
     </row>
     <row r="29">
@@ -1664,7 +1892,16 @@
         <v>37.9333395514173</v>
       </c>
       <c r="M29" t="n">
-        <v>3.729111697449429</v>
+        <v>3.700086430423509</v>
+      </c>
+      <c r="N29" t="n">
+        <v>40.73</v>
+      </c>
+      <c r="O29" t="n">
+        <v>29.51</v>
+      </c>
+      <c r="P29" t="n">
+        <v>41.29</v>
       </c>
     </row>
     <row r="30">
@@ -1707,7 +1944,16 @@
         <v>38.3740439760816</v>
       </c>
       <c r="M30" t="n">
-        <v>3.729111697449429</v>
+        <v>3.700086430423509</v>
+      </c>
+      <c r="N30" t="n">
+        <v>39.87</v>
+      </c>
+      <c r="O30" t="n">
+        <v>28.71</v>
+      </c>
+      <c r="P30" t="n">
+        <v>38.08</v>
       </c>
     </row>
     <row r="31">
@@ -1750,7 +1996,16 @@
         <v>38.8191861872791</v>
       </c>
       <c r="M31" t="n">
-        <v>3.729111697449429</v>
+        <v>3.700086430423509</v>
+      </c>
+      <c r="N31" t="n">
+        <v>38.91</v>
+      </c>
+      <c r="O31" t="n">
+        <v>26.68</v>
+      </c>
+      <c r="P31" t="n">
+        <v>38.54</v>
       </c>
     </row>
     <row r="32">
@@ -1793,7 +2048,16 @@
         <v>39.1734368360905</v>
       </c>
       <c r="M32" t="n">
-        <v>3.729111697449429</v>
+        <v>3.700086430423509</v>
+      </c>
+      <c r="N32" t="n">
+        <v>36.44</v>
+      </c>
+      <c r="O32" t="n">
+        <v>26.28</v>
+      </c>
+      <c r="P32" t="n">
+        <v>39.67</v>
       </c>
     </row>
   </sheetData>
